--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260702.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260702.xlsx
@@ -601,44 +601,44 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>168,841,000</t>
+          <t>894,744,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.24%</t>
+          <t>10.25%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>889,744,000</t>
+          <t>168,841,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.24%</t>
+          <t>10.21%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.74%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>184,380,000</t>
+          <t>184,786,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>5.01%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>4,979,000</t>
+          <t>4,999,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.56%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.41%</t>
         </is>
       </c>
     </row>
@@ -787,166 +787,166 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>94,788,442</t>
+          <t>96,288,442</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>569,427,000</t>
+          <t>25,944,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>25,824,000</t>
+          <t>569,427,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>1,872</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.79%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>30,866,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>30,666,000</t>
+          <t>134,019,945</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>134,019,945</t>
+          <t>343,589,964</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>343,589,964</t>
+          <t>1,695</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>130,597,000</t>
+          <t>131,297,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>145,692,000</t>
+          <t>146,892,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>98,567,000</t>
+          <t>99,167,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>364,675,000</t>
+          <t>367,675,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.21%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>80,288,000</t>
+          <t>80,788,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>272,366,000</t>
+          <t>274,866,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.98%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.97%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>14,343,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>14,443,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>1.86%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.67%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>10,818,453,885</t>
+          <t>9,144,193,710</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>7,220,073,096</t>
+          <t>6,997,981,743</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-450,375,379</t>
+          <t>-516,639,761</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
